--- a/06_RQ4_Direct_LLM_vs_Calibrated_GA.xlsx
+++ b/06_RQ4_Direct_LLM_vs_Calibrated_GA.xlsx
@@ -2117,22 +2117,22 @@
         <x:v>Raw Surrogate AE</x:v>
       </x:c>
       <x:c r="X1" s="12" t="str">
-        <x:v>Domain Score</x:v>
+        <x:v>AD Score</x:v>
       </x:c>
       <x:c r="Y1" s="12" t="str">
-        <x:v>Ecosystem Score</x:v>
+        <x:v>DE Score</x:v>
       </x:c>
       <x:c r="Z1" s="12" t="str">
-        <x:v>Language Score</x:v>
+        <x:v>PL Score</x:v>
       </x:c>
       <x:c r="AA1" s="12" t="str">
-        <x:v>Domain MUST Valid</x:v>
+        <x:v>AD MUST Valid</x:v>
       </x:c>
       <x:c r="AB1" s="12" t="str">
-        <x:v>Ecosystem MUST Valid</x:v>
+        <x:v>DE MUST Valid</x:v>
       </x:c>
       <x:c r="AC1" s="12" t="str">
-        <x:v>Language MUST Valid</x:v>
+        <x:v>PL MUST Valid</x:v>
       </x:c>
       <x:c r="AD1" s="12" t="str">
         <x:v>All MUST Valid</x:v>
@@ -2159,58 +2159,58 @@
         <x:v>Project Count</x:v>
       </x:c>
       <x:c r="AL1" s="12" t="str">
-        <x:v>Domain MUST Covered</x:v>
+        <x:v>AD MUST Covered</x:v>
       </x:c>
       <x:c r="AM1" s="12" t="str">
-        <x:v>Domain MUST Total</x:v>
+        <x:v>AD MUST Total</x:v>
       </x:c>
       <x:c r="AN1" s="12" t="str">
-        <x:v>Ecosystem MUST Covered</x:v>
+        <x:v>DE MUST Covered</x:v>
       </x:c>
       <x:c r="AO1" s="12" t="str">
-        <x:v>Ecosystem MUST Total</x:v>
+        <x:v>DE MUST Total</x:v>
       </x:c>
       <x:c r="AP1" s="12" t="str">
-        <x:v>Language MUST Covered</x:v>
+        <x:v>PL MUST Covered</x:v>
       </x:c>
       <x:c r="AQ1" s="12" t="str">
-        <x:v>Language MUST Total</x:v>
+        <x:v>PL MUST Total</x:v>
       </x:c>
       <x:c r="AR1" s="12" t="str">
-        <x:v>Domain SHOULD Covered</x:v>
+        <x:v>AD SHOULD Covered</x:v>
       </x:c>
       <x:c r="AS1" s="12" t="str">
-        <x:v>Domain SHOULD Total</x:v>
+        <x:v>AD SHOULD Total</x:v>
       </x:c>
       <x:c r="AT1" s="12" t="str">
-        <x:v>Ecosystem SHOULD Covered</x:v>
+        <x:v>DE SHOULD Covered</x:v>
       </x:c>
       <x:c r="AU1" s="12" t="str">
-        <x:v>Ecosystem SHOULD Total</x:v>
+        <x:v>DE SHOULD Total</x:v>
       </x:c>
       <x:c r="AV1" s="12" t="str">
-        <x:v>Language SHOULD Covered</x:v>
+        <x:v>PL SHOULD Covered</x:v>
       </x:c>
       <x:c r="AW1" s="12" t="str">
-        <x:v>Language SHOULD Total</x:v>
+        <x:v>PL SHOULD Total</x:v>
       </x:c>
       <x:c r="AX1" s="12" t="str">
-        <x:v>Domain COULD Covered</x:v>
+        <x:v>AD COULD Covered</x:v>
       </x:c>
       <x:c r="AY1" s="12" t="str">
-        <x:v>Domain COULD Total</x:v>
+        <x:v>AD COULD Total</x:v>
       </x:c>
       <x:c r="AZ1" s="12" t="str">
-        <x:v>Ecosystem COULD Covered</x:v>
+        <x:v>DE COULD Covered</x:v>
       </x:c>
       <x:c r="BA1" s="12" t="str">
-        <x:v>Ecosystem COULD Total</x:v>
+        <x:v>DE COULD Total</x:v>
       </x:c>
       <x:c r="BB1" s="12" t="str">
-        <x:v>Language COULD Covered</x:v>
+        <x:v>PL COULD Covered</x:v>
       </x:c>
       <x:c r="BC1" s="12" t="str">
-        <x:v>Language COULD Total</x:v>
+        <x:v>PL COULD Total</x:v>
       </x:c>
       <x:c r="BD1" s="12" t="str">
         <x:v>MUST Coverage Summary</x:v>
@@ -5262,7 +5262,7 @@
         <x:v>P439</x:v>
       </x:c>
       <x:c r="C2" s="60" t="str">
-        <x:v>Personal Print AI</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="D2" s="60" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5348,7 +5348,7 @@
         <x:v>P454</x:v>
       </x:c>
       <x:c r="C3" s="63" t="str">
-        <x:v>AITeams</x:v>
+        <x:v>P10</x:v>
       </x:c>
       <x:c r="D3" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5434,7 +5434,7 @@
         <x:v>P455</x:v>
       </x:c>
       <x:c r="C4" s="63" t="str">
-        <x:v>InsPOS</x:v>
+        <x:v>P11</x:v>
       </x:c>
       <x:c r="D4" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5520,7 +5520,7 @@
         <x:v>P460</x:v>
       </x:c>
       <x:c r="C5" s="63" t="str">
-        <x:v>SmartTwin</x:v>
+        <x:v>P12</x:v>
       </x:c>
       <x:c r="D5" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5606,7 +5606,7 @@
         <x:v>P461</x:v>
       </x:c>
       <x:c r="C6" s="63" t="str">
-        <x:v>DECSy</x:v>
+        <x:v>P13</x:v>
       </x:c>
       <x:c r="D6" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5692,7 +5692,7 @@
         <x:v>P462</x:v>
       </x:c>
       <x:c r="C7" s="63" t="str">
-        <x:v>Nexus</x:v>
+        <x:v>P14</x:v>
       </x:c>
       <x:c r="D7" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5778,7 +5778,7 @@
         <x:v>P466</x:v>
       </x:c>
       <x:c r="C8" s="63" t="str">
-        <x:v>LLM Agents</x:v>
+        <x:v>P15</x:v>
       </x:c>
       <x:c r="D8" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5864,7 +5864,7 @@
         <x:v>P467</x:v>
       </x:c>
       <x:c r="C9" s="63" t="str">
-        <x:v>LT-IA</x:v>
+        <x:v>P16</x:v>
       </x:c>
       <x:c r="D9" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -5950,7 +5950,7 @@
         <x:v>P440</x:v>
       </x:c>
       <x:c r="C10" s="63" t="str">
-        <x:v>2025_PrintAI Anomaly Threat Detection and Remediation</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="D10" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6036,7 +6036,7 @@
         <x:v>P441</x:v>
       </x:c>
       <x:c r="C11" s="63" t="str">
-        <x:v>XControl</x:v>
+        <x:v>P3</x:v>
       </x:c>
       <x:c r="D11" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6122,7 +6122,7 @@
         <x:v>P443</x:v>
       </x:c>
       <x:c r="C12" s="63" t="str">
-        <x:v>Pothole Detector</x:v>
+        <x:v>P4</x:v>
       </x:c>
       <x:c r="D12" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6208,7 +6208,7 @@
         <x:v>P444</x:v>
       </x:c>
       <x:c r="C13" s="63" t="str">
-        <x:v>GTQ</x:v>
+        <x:v>P5</x:v>
       </x:c>
       <x:c r="D13" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6294,7 +6294,7 @@
         <x:v>P445</x:v>
       </x:c>
       <x:c r="C14" s="63" t="str">
-        <x:v>EnergySense</x:v>
+        <x:v>P6</x:v>
       </x:c>
       <x:c r="D14" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6380,7 +6380,7 @@
         <x:v>P447</x:v>
       </x:c>
       <x:c r="C15" s="63" t="str">
-        <x:v>VRR Vulnerability Resolution and Recommendation</x:v>
+        <x:v>P7</x:v>
       </x:c>
       <x:c r="D15" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6466,7 +6466,7 @@
         <x:v>P449</x:v>
       </x:c>
       <x:c r="C16" s="63" t="str">
-        <x:v>EGRID</x:v>
+        <x:v>P8</x:v>
       </x:c>
       <x:c r="D16" s="63" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
@@ -6552,7 +6552,7 @@
         <x:v>P453</x:v>
       </x:c>
       <x:c r="C17" s="66" t="str">
-        <x:v>2025_RedePatas</x:v>
+        <x:v>P9</x:v>
       </x:c>
       <x:c r="D17" s="66" t="str">
         <x:v>GA_CALIBRADO_CCC</x:v>
